--- a/plan_data/出货计划.xlsx
+++ b/plan_data/出货计划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17120"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="SEMAXE-US" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
     <t>四毛巾</t>
   </si>
   <si>
-    <t>十二毛巾-6</t>
+    <t>六毛巾</t>
   </si>
   <si>
     <t>八件套</t>
@@ -65,19 +65,19 @@
     <t>蓝</t>
   </si>
   <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>印象</t>
-  </si>
-  <si>
     <t>海滩</t>
   </si>
   <si>
     <t>梅园</t>
   </si>
   <si>
+    <t>麦田</t>
+  </si>
+  <si>
     <t>黄灰</t>
+  </si>
+  <si>
+    <t>合计</t>
   </si>
 </sst>
 </file>
@@ -1336,67 +1336,61 @@
         <v>110</v>
       </c>
       <c r="C2" s="5">
-        <v>110</v>
-      </c>
-      <c r="D2" s="5">
-        <v>30</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="D2" s="5"/>
       <c r="E2" s="5">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F2" s="5">
-        <v>90</v>
-      </c>
-      <c r="G2" s="5">
-        <v>30</v>
-      </c>
-      <c r="H2" s="5">
-        <v>20</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
     </row>
     <row r="3" ht="20.4" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="4">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="C3" s="5">
-        <v>660</v>
-      </c>
-      <c r="D3" s="5"/>
+        <v>440</v>
+      </c>
+      <c r="D3" s="5">
+        <v>128</v>
+      </c>
       <c r="E3" s="5">
         <v>100</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5">
-        <v>42</v>
-      </c>
-      <c r="H3" s="5"/>
+      <c r="F3" s="5">
+        <v>60</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" ht="20.4" spans="1:10">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="4">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="C4" s="5">
-        <v>264</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5">
-        <v>50</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="D4" s="5">
+        <v>96</v>
+      </c>
+      <c r="E4" s="5"/>
       <c r="F4" s="5">
         <v>30</v>
       </c>
-      <c r="G4" s="5">
-        <v>30</v>
-      </c>
-      <c r="H4" s="5">
-        <v>20</v>
-      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" ht="20.4" spans="1:10">
       <c r="A5" s="3" t="s">
@@ -1405,31 +1399,39 @@
       <c r="B5" s="4">
         <v>110</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5">
+        <v>154</v>
+      </c>
+      <c r="D5" s="5">
+        <v>96</v>
+      </c>
       <c r="E5" s="5">
         <v>50</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5">
-        <v>20</v>
-      </c>
+      <c r="F5" s="5">
+        <v>30</v>
+      </c>
+      <c r="G5" s="5">
+        <v>30</v>
+      </c>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" ht="20.4" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5">
-        <v>110</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B6" s="4">
+        <v>154</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5">
+        <v>50</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
         <v>30</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" ht="20.4" spans="1:10">
@@ -1438,74 +1440,76 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>154</v>
-      </c>
-      <c r="D7" s="5">
-        <v>30</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="5">
+        <v>30</v>
+      </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" ht="20.4" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5">
-        <v>110</v>
-      </c>
-      <c r="D8" s="5">
-        <v>30</v>
-      </c>
+      <c r="B8" s="5">
+        <v>132</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="5">
-        <v>50</v>
-      </c>
-      <c r="F8" s="5"/>
+        <v>80</v>
+      </c>
+      <c r="F8" s="5">
+        <v>42</v>
+      </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="5">
-        <v>20</v>
-      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" ht="20.4" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4">
-        <v>110</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="5">
+      <c r="D9" s="5"/>
+      <c r="E9" s="5">
+        <v>200</v>
+      </c>
+      <c r="F9" s="5">
         <v>30</v>
       </c>
-      <c r="E9" s="5">
-        <v>60</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="5">
+        <v>30</v>
+      </c>
       <c r="H9" s="5"/>
     </row>
     <row r="10" ht="20.4" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
+      <c r="B10" s="4">
+        <v>33</v>
+      </c>
+      <c r="C10" s="5">
+        <v>52</v>
+      </c>
       <c r="D10" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E10" s="5">
-        <v>250</v>
+        <v>63</v>
       </c>
       <c r="F10" s="5">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G10" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H10" s="5">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:10">

--- a/plan_data/出货计划.xlsx
+++ b/plan_data/出货计划.xlsx
@@ -1356,7 +1356,7 @@
         <v>110</v>
       </c>
       <c r="C3" s="5">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="D3" s="5">
         <v>128</v>
@@ -1494,7 +1494,7 @@
         <v>33</v>
       </c>
       <c r="C10" s="5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D10" s="5">
         <v>20</v>

--- a/plan_data/出货计划.xlsx
+++ b/plan_data/出货计划.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160"/>
+    <workbookView windowWidth="32460" windowHeight="16160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="SEMAXE-US" sheetId="3" r:id="rId1"/>
+    <sheet name="SEMAXE-CA" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>颜色</t>
   </si>
@@ -78,6 +79,15 @@
   </si>
   <si>
     <t>合计</t>
+  </si>
+  <si>
+    <t>十二毛巾-6</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>印象</t>
   </si>
 </sst>
 </file>
@@ -90,7 +100,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +112,14 @@
       <b/>
       <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -615,137 +633,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -755,17 +773,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1309,224 +1333,349 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="20.4" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" ht="20.4" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:10">
+      <c r="A4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" ht="20.4" spans="1:10">
+      <c r="A5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" ht="20.4" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" ht="20.4" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" ht="20.4" spans="1:10">
+      <c r="A8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" ht="20.4" spans="1:10">
+      <c r="A9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" ht="20.4" spans="1:10">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="9:10">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="7.23076923076923" customWidth="1"/>
+    <col min="2" max="2" width="9.92307692307692" customWidth="1"/>
+    <col min="3" max="3" width="12.9230769230769" customWidth="1"/>
+    <col min="4" max="4" width="15.2307692307692" customWidth="1"/>
+    <col min="5" max="5" width="9.92307692307692" customWidth="1"/>
+    <col min="6" max="7" width="12.9230769230769" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20.4" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="20.4" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="20.4" spans="1:10">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4">
-        <v>110</v>
-      </c>
-      <c r="C2" s="5">
-        <v>220</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5">
-        <v>150</v>
-      </c>
-      <c r="F2" s="5">
-        <v>66</v>
-      </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" ht="20.4" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="3">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="20.4" spans="1:7">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4">
-        <v>110</v>
-      </c>
-      <c r="C3" s="5">
-        <v>484</v>
-      </c>
-      <c r="D3" s="5">
-        <v>128</v>
-      </c>
-      <c r="E3" s="5">
-        <v>100</v>
-      </c>
-      <c r="F3" s="5">
-        <v>60</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3">
+        <v>6</v>
+      </c>
+      <c r="E4" s="3">
+        <v>30</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" ht="20.4" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" ht="20.4" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="4">
-        <v>110</v>
-      </c>
-      <c r="C4" s="5">
-        <v>220</v>
-      </c>
-      <c r="D4" s="5">
-        <v>96</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5">
+      <c r="D5" s="3">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3">
         <v>30</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" ht="20.4" spans="1:10">
-      <c r="A5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="4">
-        <v>110</v>
-      </c>
-      <c r="C5" s="5">
-        <v>154</v>
-      </c>
-      <c r="D5" s="5">
-        <v>96</v>
-      </c>
-      <c r="E5" s="5">
-        <v>50</v>
-      </c>
-      <c r="F5" s="5">
-        <v>30</v>
-      </c>
-      <c r="G5" s="5">
-        <v>30</v>
-      </c>
-      <c r="H5" s="5"/>
-    </row>
-    <row r="6" ht="20.4" spans="1:10">
-      <c r="A6" s="3" t="s">
+      <c r="F5" s="3">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" ht="20.4" spans="1:7">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3">
+        <v>6</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row r="7" ht="20.4" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" ht="20.4" spans="1:7">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4">
-        <v>154</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5">
-        <v>50</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5">
-        <v>30</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" ht="20.4" spans="1:10">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" ht="20.4" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5">
-        <v>110</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5">
-        <v>30</v>
-      </c>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" ht="20.4" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="5">
-        <v>132</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5">
-        <v>80</v>
-      </c>
-      <c r="F8" s="5">
-        <v>42</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" ht="20.4" spans="1:10">
-      <c r="A9" s="3" t="s">
+      <c r="B9" s="3">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3">
+        <v>22</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" ht="20.4" spans="1:7">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5">
-        <v>200</v>
-      </c>
-      <c r="F9" s="5">
-        <v>30</v>
-      </c>
-      <c r="G9" s="5">
-        <v>30</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" ht="20.4" spans="1:10">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4">
-        <v>33</v>
-      </c>
-      <c r="C10" s="5">
-        <v>54</v>
-      </c>
-      <c r="D10" s="5">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5">
-        <v>43</v>
-      </c>
-      <c r="G10" s="5">
-        <v>20</v>
-      </c>
-      <c r="H10" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="9:10">
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan_data/出货计划.xlsx
+++ b/plan_data/出货计划.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32460" windowHeight="16160" activeTab="1"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="SEMAXE-US" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
   <si>
     <t>颜色</t>
   </si>
@@ -39,55 +39,55 @@
     <t>四毛巾</t>
   </si>
   <si>
-    <t>六毛巾</t>
+    <t>十二毛巾-10</t>
+  </si>
+  <si>
+    <t>十二毛巾-6</t>
+  </si>
+  <si>
+    <t>八件套-6</t>
+  </si>
+  <si>
+    <t>八件套-10</t>
+  </si>
+  <si>
+    <t>四浴巾</t>
+  </si>
+  <si>
+    <t>十二件套</t>
+  </si>
+  <si>
+    <t>十八件套</t>
+  </si>
+  <si>
+    <t>黄</t>
+  </si>
+  <si>
+    <t>灰</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>蓝</t>
+  </si>
+  <si>
+    <t>紫</t>
+  </si>
+  <si>
+    <t>印象</t>
+  </si>
+  <si>
+    <t>海滩</t>
+  </si>
+  <si>
+    <t>黄灰</t>
+  </si>
+  <si>
+    <t>十二毛巾</t>
   </si>
   <si>
     <t>八件套</t>
-  </si>
-  <si>
-    <t>四浴巾</t>
-  </si>
-  <si>
-    <t>十二件套</t>
-  </si>
-  <si>
-    <t>十八件套</t>
-  </si>
-  <si>
-    <t>黄</t>
-  </si>
-  <si>
-    <t>灰</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>海滩</t>
-  </si>
-  <si>
-    <t>梅园</t>
-  </si>
-  <si>
-    <t>麦田</t>
-  </si>
-  <si>
-    <t>黄灰</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>十二毛巾-6</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>印象</t>
   </si>
 </sst>
 </file>
@@ -100,7 +100,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,14 +118,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -143,12 +135,35 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -633,137 +648,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,16 +788,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -790,6 +799,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1316,165 +1334,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="7.23076923076923" customWidth="1"/>
     <col min="2" max="2" width="12.9230769230769" customWidth="1"/>
-    <col min="3" max="6" width="11.1538461538462" customWidth="1"/>
-    <col min="7" max="8" width="14.6153846153846" customWidth="1"/>
-    <col min="9" max="10" width="12.9230769230769" customWidth="1"/>
+    <col min="3" max="3" width="11.1538461538462" customWidth="1"/>
+    <col min="4" max="4" width="19.0769230769231" customWidth="1"/>
+    <col min="5" max="5" width="17.3846153846154" customWidth="1"/>
+    <col min="6" max="6" width="13.9230769230769" customWidth="1"/>
+    <col min="7" max="7" width="15.6153846153846" customWidth="1"/>
+    <col min="8" max="8" width="11.1538461538462" customWidth="1"/>
+    <col min="9" max="10" width="14.6153846153846" customWidth="1"/>
+    <col min="11" max="12" width="12.9230769230769" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.2" spans="1:10">
+    <row r="1" ht="23.2" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="20.4" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" ht="20.4" spans="1:10">
-      <c r="A3" s="6" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" ht="20.4" spans="1:10">
-      <c r="A4" s="6" t="s">
+    </row>
+    <row r="2" ht="20.4" spans="1:12">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" ht="20.4" spans="1:10">
-      <c r="A5" s="6" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="5">
+        <v>260</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5">
+        <v>150</v>
+      </c>
+      <c r="H2" s="5">
+        <v>228</v>
+      </c>
+      <c r="I2" s="5"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" ht="20.4" spans="1:12">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" ht="20.4" spans="1:10">
-      <c r="A6" s="6" t="s">
+      <c r="B3" s="7">
+        <v>140</v>
+      </c>
+      <c r="C3" s="5">
+        <v>520</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5">
+        <v>120</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5">
+        <v>42</v>
+      </c>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:12">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" ht="20.4" spans="1:10">
-      <c r="A7" s="6" t="s">
+      <c r="B4" s="7">
+        <v>160</v>
+      </c>
+      <c r="C4" s="5">
+        <v>160</v>
+      </c>
+      <c r="D4" s="5">
+        <v>50</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5">
+        <v>70</v>
+      </c>
+      <c r="H4" s="8">
+        <v>96</v>
+      </c>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" ht="20.4" spans="1:12">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" ht="20.4" spans="1:10">
-      <c r="A8" s="6" t="s">
+      <c r="B5" s="4">
+        <v>100</v>
+      </c>
+      <c r="C5" s="5">
+        <v>220</v>
+      </c>
+      <c r="E5" s="5">
+        <v>36</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
+        <v>50</v>
+      </c>
+      <c r="H5" s="5">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8">
+        <v>30</v>
+      </c>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" ht="20.4" spans="1:12">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-    </row>
-    <row r="9" ht="20.4" spans="1:10">
-      <c r="A9" s="6" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5">
+        <v>100</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <v>50</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" ht="20.4" spans="1:12">
+      <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" ht="20.4" spans="1:10">
-      <c r="A10" s="6" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>120</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" ht="20.4" spans="1:12">
+      <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-    </row>
-    <row r="17" spans="9:10">
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5">
+        <v>30</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" ht="20.4" spans="1:12">
+      <c r="A9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="4">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5">
+        <v>100</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
+        <v>150</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5">
+        <v>30</v>
+      </c>
+      <c r="J9" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1486,196 +1572,138 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="6"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.23076923076923" customWidth="1"/>
-    <col min="2" max="2" width="9.92307692307692" customWidth="1"/>
-    <col min="3" max="3" width="12.9230769230769" customWidth="1"/>
-    <col min="4" max="4" width="15.2307692307692" customWidth="1"/>
-    <col min="5" max="5" width="9.92307692307692" customWidth="1"/>
-    <col min="6" max="7" width="12.9230769230769" customWidth="1"/>
+    <col min="2" max="2" width="12.9230769230769" customWidth="1"/>
+    <col min="3" max="3" width="11.1538461538462" customWidth="1"/>
+    <col min="4" max="4" width="14.6153846153846" customWidth="1"/>
+    <col min="5" max="6" width="11.1538461538462" customWidth="1"/>
+    <col min="7" max="8" width="14.6153846153846" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" spans="1:7">
+    <row r="1" ht="23.2" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="20.4" spans="1:8">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" ht="20.4" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" ht="20.4" spans="1:8">
+      <c r="A4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="6"/>
+    </row>
+    <row r="5" ht="20.4" spans="1:8">
+      <c r="A5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" ht="20.4" spans="1:8">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" ht="20.4" spans="1:8">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" ht="20.4" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="6"/>
+    </row>
+    <row r="9" ht="20.4" spans="1:8">
+      <c r="A9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="20.4" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3">
-        <v>20</v>
-      </c>
-      <c r="F2" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" ht="20.4" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3">
-        <v>6</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="20.4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>6</v>
-      </c>
-      <c r="E4" s="3">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" ht="20.4" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3">
-        <v>6</v>
-      </c>
-      <c r="G5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" ht="20.4" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" ht="20.4" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" ht="20.4" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3">
-        <v>6</v>
-      </c>
-      <c r="E8" s="3">
-        <v>20</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" ht="20.4" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3">
-        <v>22</v>
-      </c>
-      <c r="D9" s="3">
-        <v>6</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" ht="20.4" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" spans="2:3">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
